--- a/iwpb-sg-dashboard/sample/IWPB_FiveGroups_Driller.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_FiveGroups_Driller.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IWPB India" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CIB Singapore" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HK" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corp Centre" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IWPB France" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CIB Singapore" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corp Centre" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2634,94 +2635,94 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>88.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="L3" t="n">
-        <v>59.4</v>
+        <v>27</v>
       </c>
       <c r="M3" t="n">
-        <v>78.7</v>
+        <v>35.8</v>
       </c>
       <c r="N3" t="n">
-        <v>79.40000000000001</v>
+        <v>36.1</v>
       </c>
       <c r="O3" t="n">
-        <v>47.3</v>
+        <v>21.5</v>
       </c>
       <c r="P3" t="n">
-        <v>47.1</v>
+        <v>21.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>55.7</v>
+        <v>25.3</v>
       </c>
       <c r="R3" t="n">
-        <v>80.8</v>
+        <v>36.7</v>
       </c>
       <c r="S3" t="n">
-        <v>86.09999999999999</v>
+        <v>39.2</v>
       </c>
       <c r="T3" t="n">
-        <v>51.6</v>
+        <v>23.5</v>
       </c>
       <c r="U3" t="n">
-        <v>82.8</v>
+        <v>37.6</v>
       </c>
       <c r="V3" t="n">
-        <v>63.2</v>
+        <v>28.7</v>
       </c>
       <c r="W3" t="n">
-        <v>58.9</v>
+        <v>26.8</v>
       </c>
       <c r="X3" t="n">
-        <v>56.8</v>
+        <v>25.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>59.9</v>
+        <v>27.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>39.4</v>
+        <v>17.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>50.6</v>
+        <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>47.4</v>
+        <v>21.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>71</v>
+        <v>32.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>92.90000000000001</v>
+        <v>42.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>101.7</v>
+        <v>46.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>59.7</v>
+        <v>27.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>40.8</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>58.7</v>
+        <v>26.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>400.3</v>
+        <v>182</v>
       </c>
       <c r="AJ3" t="n">
-        <v>313</v>
+        <v>142.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>306.3</v>
+        <v>139.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>820.5</v>
+        <v>373</v>
       </c>
       <c r="AM3" t="n">
-        <v>737.8</v>
+        <v>335.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>780.1</v>
+        <v>354.4</v>
       </c>
     </row>
     <row r="4">
@@ -2776,94 +2777,94 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>79.2</v>
+        <v>36</v>
       </c>
       <c r="L4" t="n">
-        <v>73.90000000000001</v>
+        <v>33.6</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>20.5</v>
       </c>
       <c r="N4" t="n">
-        <v>59.6</v>
+        <v>27.1</v>
       </c>
       <c r="O4" t="n">
-        <v>63.5</v>
+        <v>28.9</v>
       </c>
       <c r="P4" t="n">
-        <v>67</v>
+        <v>30.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>68.5</v>
+        <v>31.1</v>
       </c>
       <c r="R4" t="n">
-        <v>62.2</v>
+        <v>28.3</v>
       </c>
       <c r="S4" t="n">
-        <v>69.3</v>
+        <v>31.5</v>
       </c>
       <c r="T4" t="n">
-        <v>58.9</v>
+        <v>26.8</v>
       </c>
       <c r="U4" t="n">
-        <v>54.8</v>
+        <v>24.9</v>
       </c>
       <c r="V4" t="n">
-        <v>87</v>
+        <v>39.5</v>
       </c>
       <c r="W4" t="n">
-        <v>71.59999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="X4" t="n">
-        <v>72.59999999999999</v>
+        <v>33</v>
       </c>
       <c r="Y4" t="n">
-        <v>45.5</v>
+        <v>20.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>64.5</v>
+        <v>29.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>77.7</v>
+        <v>35.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>49.5</v>
+        <v>22.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>81.40000000000001</v>
+        <v>37</v>
       </c>
       <c r="AD4" t="n">
-        <v>61.6</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>72.09999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>65</v>
+        <v>29.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>69.7</v>
+        <v>31.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>82.8</v>
+        <v>37.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>388.2</v>
+        <v>176.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>381.4</v>
+        <v>173.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>371.8</v>
+        <v>168.9</v>
       </c>
       <c r="AL4" t="n">
-        <v>788.9</v>
+        <v>358.7</v>
       </c>
       <c r="AM4" t="n">
-        <v>814</v>
+        <v>369.9</v>
       </c>
       <c r="AN4" t="n">
-        <v>840.1</v>
+        <v>381.8</v>
       </c>
     </row>
     <row r="5">
@@ -2918,94 +2919,94 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>68.09999999999999</v>
+        <v>30.9</v>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>21.3</v>
       </c>
       <c r="M5" t="n">
-        <v>55.2</v>
+        <v>25.1</v>
       </c>
       <c r="N5" t="n">
-        <v>70.40000000000001</v>
+        <v>32</v>
       </c>
       <c r="O5" t="n">
-        <v>74</v>
+        <v>33.6</v>
       </c>
       <c r="P5" t="n">
-        <v>38.4</v>
+        <v>17.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>65.59999999999999</v>
+        <v>29.8</v>
       </c>
       <c r="R5" t="n">
-        <v>82</v>
+        <v>37.3</v>
       </c>
       <c r="S5" t="n">
-        <v>73.8</v>
+        <v>33.6</v>
       </c>
       <c r="T5" t="n">
-        <v>56.7</v>
+        <v>25.8</v>
       </c>
       <c r="U5" t="n">
-        <v>52.4</v>
+        <v>23.8</v>
       </c>
       <c r="V5" t="n">
-        <v>56</v>
+        <v>25.5</v>
       </c>
       <c r="W5" t="n">
-        <v>48.2</v>
+        <v>21.9</v>
       </c>
       <c r="X5" t="n">
-        <v>58.8</v>
+        <v>26.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>59.7</v>
+        <v>27.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>60.2</v>
+        <v>27.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>76.09999999999999</v>
+        <v>34.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>59.2</v>
+        <v>26.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>44.6</v>
+        <v>20.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>74.5</v>
+        <v>33.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>49.2</v>
+        <v>22.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>56.7</v>
+        <v>25.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>60.4</v>
+        <v>27.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>57.9</v>
+        <v>26.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>353</v>
+        <v>160.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>362.2</v>
+        <v>164.7</v>
       </c>
       <c r="AK5" t="n">
-        <v>363.9</v>
+        <v>165.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>739.5</v>
+        <v>336.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>705.5</v>
+        <v>320.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>697</v>
+        <v>316.9</v>
       </c>
     </row>
     <row r="6">
@@ -3060,94 +3061,94 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>68.2</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>85.8</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>80.5</v>
+        <v>36.6</v>
       </c>
       <c r="N6" t="n">
-        <v>80.8</v>
+        <v>36.7</v>
       </c>
       <c r="O6" t="n">
-        <v>82.2</v>
+        <v>37.3</v>
       </c>
       <c r="P6" t="n">
-        <v>42.5</v>
+        <v>19.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>26.3</v>
       </c>
       <c r="R6" t="n">
-        <v>71.90000000000001</v>
+        <v>32.7</v>
       </c>
       <c r="S6" t="n">
-        <v>77.09999999999999</v>
+        <v>35</v>
       </c>
       <c r="T6" t="n">
-        <v>88.2</v>
+        <v>40.1</v>
       </c>
       <c r="U6" t="n">
-        <v>76.7</v>
+        <v>34.8</v>
       </c>
       <c r="V6" t="n">
-        <v>66.7</v>
+        <v>30.3</v>
       </c>
       <c r="W6" t="n">
-        <v>79.90000000000001</v>
+        <v>36.3</v>
       </c>
       <c r="X6" t="n">
-        <v>76.40000000000001</v>
+        <v>34.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>82.8</v>
+        <v>37.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>88.8</v>
+        <v>40.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>74.59999999999999</v>
+        <v>33.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>68</v>
+        <v>30.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>67.40000000000001</v>
+        <v>30.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>94.7</v>
+        <v>43.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>97.3</v>
+        <v>44.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>93.3</v>
+        <v>42.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>91.40000000000001</v>
+        <v>41.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>91</v>
+        <v>41.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>440</v>
+        <v>199.9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>470.5</v>
+        <v>213.8</v>
       </c>
       <c r="AK6" t="n">
-        <v>456.4</v>
+        <v>207.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>878.6</v>
+        <v>399.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>1005.6</v>
+        <v>457</v>
       </c>
       <c r="AN6" t="n">
-        <v>963</v>
+        <v>437.7</v>
       </c>
     </row>
     <row r="7">
@@ -3202,94 +3203,94 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>47.8</v>
+        <v>21.7</v>
       </c>
       <c r="L7" t="n">
-        <v>64.09999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="M7" t="n">
-        <v>49.5</v>
+        <v>22.5</v>
       </c>
       <c r="N7" t="n">
-        <v>54.8</v>
+        <v>24.9</v>
       </c>
       <c r="O7" t="n">
-        <v>60.5</v>
+        <v>27.5</v>
       </c>
       <c r="P7" t="n">
-        <v>71.2</v>
+        <v>32.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>47.1</v>
+        <v>21.4</v>
       </c>
       <c r="R7" t="n">
-        <v>45.5</v>
+        <v>20.7</v>
       </c>
       <c r="S7" t="n">
-        <v>65.2</v>
+        <v>29.6</v>
       </c>
       <c r="T7" t="n">
-        <v>43.6</v>
+        <v>19.8</v>
       </c>
       <c r="U7" t="n">
-        <v>61.1</v>
+        <v>27.8</v>
       </c>
       <c r="V7" t="n">
-        <v>49.6</v>
+        <v>22.6</v>
       </c>
       <c r="W7" t="n">
-        <v>56</v>
+        <v>25.4</v>
       </c>
       <c r="X7" t="n">
-        <v>36.8</v>
+        <v>16.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>65.09999999999999</v>
+        <v>29.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>51.5</v>
+        <v>23.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>47.1</v>
+        <v>21.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>80.40000000000001</v>
+        <v>36.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>65.09999999999999</v>
+        <v>29.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>96.40000000000001</v>
+        <v>43.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>61.7</v>
+        <v>28.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>53.2</v>
+        <v>24.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>58.4</v>
+        <v>26.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>75.09999999999999</v>
+        <v>34.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>347.9</v>
+        <v>158.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>336.9</v>
+        <v>153.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>327.2</v>
+        <v>148.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>660</v>
+        <v>300.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>746.8</v>
+        <v>339.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>704.7</v>
+        <v>320.3</v>
       </c>
     </row>
     <row r="8">
@@ -3344,94 +3345,94 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>67.7</v>
+        <v>30.8</v>
       </c>
       <c r="L8" t="n">
-        <v>59.3</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n">
-        <v>49.5</v>
+        <v>22.5</v>
       </c>
       <c r="N8" t="n">
-        <v>77.5</v>
+        <v>35.2</v>
       </c>
       <c r="O8" t="n">
-        <v>74.7</v>
+        <v>34</v>
       </c>
       <c r="P8" t="n">
-        <v>66.90000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>54</v>
+        <v>24.5</v>
       </c>
       <c r="R8" t="n">
-        <v>39.5</v>
+        <v>18</v>
       </c>
       <c r="S8" t="n">
-        <v>72.40000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="T8" t="n">
-        <v>64.7</v>
+        <v>29.4</v>
       </c>
       <c r="U8" t="n">
-        <v>43.7</v>
+        <v>19.9</v>
       </c>
       <c r="V8" t="n">
-        <v>65.2</v>
+        <v>29.6</v>
       </c>
       <c r="W8" t="n">
-        <v>47</v>
+        <v>21.4</v>
       </c>
       <c r="X8" t="n">
-        <v>66.7</v>
+        <v>30.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>69</v>
+        <v>31.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.8</v>
+        <v>32.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>69.90000000000001</v>
+        <v>31.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>69.3</v>
+        <v>31.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>52</v>
+        <v>23.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>62</v>
+        <v>28.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>60.3</v>
+        <v>27.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>64</v>
+        <v>29.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>70.59999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>75.2</v>
+        <v>34.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>395.6</v>
+        <v>179.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>393.7</v>
+        <v>178.9</v>
       </c>
       <c r="AK8" t="n">
-        <v>409.8</v>
+        <v>186.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>735.1</v>
+        <v>334.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>777.8</v>
+        <v>353.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>831.2</v>
+        <v>377.9</v>
       </c>
     </row>
     <row r="9">
@@ -3486,94 +3487,94 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-43.9</v>
+        <v>-21.9</v>
       </c>
       <c r="L9" t="n">
-        <v>-35.8</v>
+        <v>-17.9</v>
       </c>
       <c r="M9" t="n">
-        <v>-20.2</v>
+        <v>-10.1</v>
       </c>
       <c r="N9" t="n">
-        <v>-32.6</v>
+        <v>-16.3</v>
       </c>
       <c r="O9" t="n">
-        <v>-27</v>
+        <v>-13.5</v>
       </c>
       <c r="P9" t="n">
-        <v>-36.1</v>
+        <v>-18.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>-23.8</v>
+        <v>-11.9</v>
       </c>
       <c r="R9" t="n">
-        <v>-29.5</v>
+        <v>-14.8</v>
       </c>
       <c r="S9" t="n">
-        <v>-29.4</v>
+        <v>-14.7</v>
       </c>
       <c r="T9" t="n">
-        <v>-29.6</v>
+        <v>-14.8</v>
       </c>
       <c r="U9" t="n">
-        <v>-26.6</v>
+        <v>-13.3</v>
       </c>
       <c r="V9" t="n">
-        <v>-19.1</v>
+        <v>-9.5</v>
       </c>
       <c r="W9" t="n">
-        <v>-31.2</v>
+        <v>-15.6</v>
       </c>
       <c r="X9" t="n">
-        <v>-34.4</v>
+        <v>-17.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
       <c r="Z9" t="n">
-        <v>-22.3</v>
+        <v>-11.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>-29.6</v>
+        <v>-14.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>-31.8</v>
+        <v>-15.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>-27.3</v>
+        <v>-13.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>-28.3</v>
+        <v>-14.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>-36.9</v>
+        <v>-18.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>-21.7</v>
+        <v>-10.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>-16.9</v>
+        <v>-8.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>-195.6</v>
+        <v>-97.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-177.3</v>
+        <v>-88.59999999999999</v>
       </c>
       <c r="AK9" t="n">
-        <v>-180.1</v>
+        <v>-90</v>
       </c>
       <c r="AL9" t="n">
-        <v>-353.6</v>
+        <v>-176.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>-333.4</v>
+        <v>-166.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>-328.9</v>
+        <v>-164.5</v>
       </c>
     </row>
     <row r="10">
@@ -3628,94 +3629,94 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-34.6</v>
+        <v>-17.3</v>
       </c>
       <c r="L10" t="n">
-        <v>-24.4</v>
+        <v>-12.2</v>
       </c>
       <c r="M10" t="n">
-        <v>-24.9</v>
+        <v>-12.4</v>
       </c>
       <c r="N10" t="n">
-        <v>-36.6</v>
+        <v>-18.3</v>
       </c>
       <c r="O10" t="n">
-        <v>-25.1</v>
+        <v>-12.6</v>
       </c>
       <c r="P10" t="n">
-        <v>-16.6</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-27.5</v>
+        <v>-13.7</v>
       </c>
       <c r="R10" t="n">
-        <v>-20.7</v>
+        <v>-10.3</v>
       </c>
       <c r="S10" t="n">
-        <v>-33.8</v>
+        <v>-16.9</v>
       </c>
       <c r="T10" t="n">
-        <v>-19.1</v>
+        <v>-9.5</v>
       </c>
       <c r="U10" t="n">
-        <v>-22.5</v>
+        <v>-11.2</v>
       </c>
       <c r="V10" t="n">
-        <v>-17.3</v>
+        <v>-8.6</v>
       </c>
       <c r="W10" t="n">
-        <v>-26.8</v>
+        <v>-13.4</v>
       </c>
       <c r="X10" t="n">
-        <v>-21.2</v>
+        <v>-10.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>-26</v>
+        <v>-13</v>
       </c>
       <c r="Z10" t="n">
-        <v>-24.4</v>
+        <v>-12.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>-23.2</v>
+        <v>-11.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>-31.1</v>
+        <v>-15.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>-31.1</v>
+        <v>-15.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>-26.7</v>
+        <v>-13.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>-21.8</v>
+        <v>-10.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>-20.9</v>
+        <v>-10.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>-27.7</v>
+        <v>-13.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>-38.5</v>
+        <v>-19.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>-162.2</v>
+        <v>-81.09999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-152.7</v>
+        <v>-76.40000000000001</v>
       </c>
       <c r="AK10" t="n">
-        <v>-155.7</v>
+        <v>-77.90000000000001</v>
       </c>
       <c r="AL10" t="n">
-        <v>-303.1</v>
+        <v>-151.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>-319.4</v>
+        <v>-159.9</v>
       </c>
       <c r="AN10" t="n">
-        <v>-312.1</v>
+        <v>-156.3</v>
       </c>
     </row>
     <row r="11">
@@ -3770,94 +3771,94 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-21.2</v>
+        <v>-10.6</v>
       </c>
       <c r="L11" t="n">
-        <v>-25.2</v>
+        <v>-12.6</v>
       </c>
       <c r="M11" t="n">
-        <v>-33.8</v>
+        <v>-16.9</v>
       </c>
       <c r="N11" t="n">
-        <v>-26.3</v>
+        <v>-13.1</v>
       </c>
       <c r="O11" t="n">
-        <v>-23.6</v>
+        <v>-11.8</v>
       </c>
       <c r="P11" t="n">
-        <v>-17.8</v>
+        <v>-8.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>-27.4</v>
+        <v>-13.7</v>
       </c>
       <c r="R11" t="n">
-        <v>-26.2</v>
+        <v>-13.1</v>
       </c>
       <c r="S11" t="n">
-        <v>-19.8</v>
+        <v>-9.9</v>
       </c>
       <c r="T11" t="n">
-        <v>-20.6</v>
+        <v>-10.3</v>
       </c>
       <c r="U11" t="n">
-        <v>-26.1</v>
+        <v>-13</v>
       </c>
       <c r="V11" t="n">
-        <v>-31.6</v>
+        <v>-15.8</v>
       </c>
       <c r="W11" t="n">
-        <v>-30.9</v>
+        <v>-15.5</v>
       </c>
       <c r="X11" t="n">
-        <v>-28.7</v>
+        <v>-14.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>-25.9</v>
+        <v>-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>-29.3</v>
+        <v>-14.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>-27.6</v>
+        <v>-13.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>-39.1</v>
+        <v>-19.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>-21.7</v>
+        <v>-10.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>-25.7</v>
+        <v>-12.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>-34.3</v>
+        <v>-17.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>-26.2</v>
+        <v>-13.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>-35.1</v>
+        <v>-17.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>-27.4</v>
+        <v>-13.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>-147.9</v>
+        <v>-73.90000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-181.5</v>
+        <v>-90.90000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>-188.2</v>
+        <v>-94.3</v>
       </c>
       <c r="AL11" t="n">
-        <v>-299.6</v>
+        <v>-149.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>-351.9</v>
+        <v>-176.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>-331</v>
+        <v>-165.7</v>
       </c>
     </row>
     <row r="12">
@@ -3912,94 +3913,94 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-36.7</v>
+        <v>-18.3</v>
       </c>
       <c r="L12" t="n">
-        <v>-28.7</v>
+        <v>-14.3</v>
       </c>
       <c r="M12" t="n">
-        <v>-28.5</v>
+        <v>-14.2</v>
       </c>
       <c r="N12" t="n">
-        <v>-30.2</v>
+        <v>-15.1</v>
       </c>
       <c r="O12" t="n">
-        <v>-28.3</v>
+        <v>-14.1</v>
       </c>
       <c r="P12" t="n">
-        <v>-30.6</v>
+        <v>-15.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>-24.1</v>
+        <v>-12</v>
       </c>
       <c r="R12" t="n">
-        <v>-24.3</v>
+        <v>-12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>-30.4</v>
+        <v>-15.2</v>
       </c>
       <c r="T12" t="n">
-        <v>-23.6</v>
+        <v>-11.8</v>
       </c>
       <c r="U12" t="n">
-        <v>-18.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-24.3</v>
+        <v>-12.1</v>
       </c>
       <c r="W12" t="n">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="X12" t="n">
-        <v>-30.9</v>
+        <v>-15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>-24.1</v>
+        <v>-12.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>-22.4</v>
+        <v>-11.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>-26.1</v>
+        <v>-13.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>-35.7</v>
+        <v>-17.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-27.6</v>
+        <v>-13.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>-28.6</v>
+        <v>-14.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>-27.9</v>
+        <v>-13.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>-29.3</v>
+        <v>-14.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>-32.5</v>
+        <v>-16.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>-34.9</v>
+        <v>-17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>-183</v>
+        <v>-91.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-164.2</v>
+        <v>-82.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>-162</v>
+        <v>-81.09999999999999</v>
       </c>
       <c r="AL12" t="n">
-        <v>-328.3</v>
+        <v>-163.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>-345</v>
+        <v>-172.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>-364.2</v>
+        <v>-182.3</v>
       </c>
     </row>
   </sheetData>
@@ -4432,94 +4433,94 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>119</v>
+        <v>93.5</v>
       </c>
       <c r="L3" t="n">
-        <v>77.7</v>
+        <v>61.1</v>
       </c>
       <c r="M3" t="n">
-        <v>111.7</v>
+        <v>87.8</v>
       </c>
       <c r="N3" t="n">
-        <v>96</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>63.9</v>
+        <v>50.2</v>
       </c>
       <c r="P3" t="n">
-        <v>88.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>92.3</v>
+        <v>72.5</v>
       </c>
       <c r="R3" t="n">
-        <v>78.40000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="S3" t="n">
-        <v>43</v>
+        <v>33.8</v>
       </c>
       <c r="T3" t="n">
-        <v>74.90000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="U3" t="n">
-        <v>77.3</v>
+        <v>60.8</v>
       </c>
       <c r="V3" t="n">
-        <v>62.6</v>
+        <v>49.2</v>
       </c>
       <c r="W3" t="n">
-        <v>104.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>71</v>
+        <v>55.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>68.59999999999999</v>
+        <v>53.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>70.09999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>62.3</v>
+        <v>49</v>
       </c>
       <c r="AB3" t="n">
-        <v>62.4</v>
+        <v>49.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>76.40000000000001</v>
+        <v>60.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>80</v>
+        <v>62.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>66.8</v>
+        <v>52.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>73.5</v>
+        <v>57.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>52.6</v>
+        <v>41.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>83.3</v>
+        <v>65.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>556.6</v>
+        <v>437.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>438.7</v>
+        <v>344.8</v>
       </c>
       <c r="AK3" t="n">
-        <v>436.4</v>
+        <v>343</v>
       </c>
       <c r="AL3" t="n">
-        <v>985.1</v>
+        <v>774.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>871.3</v>
+        <v>684.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>842.3</v>
+        <v>661.9</v>
       </c>
     </row>
     <row r="4">
@@ -4574,94 +4575,94 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>76.59999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="L4" t="n">
-        <v>55.7</v>
+        <v>43.7</v>
       </c>
       <c r="M4" t="n">
-        <v>109.7</v>
+        <v>86.2</v>
       </c>
       <c r="N4" t="n">
-        <v>72.90000000000001</v>
+        <v>57.3</v>
       </c>
       <c r="O4" t="n">
-        <v>72.40000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="P4" t="n">
-        <v>62.7</v>
+        <v>49.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>96.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>93.8</v>
+        <v>73.7</v>
       </c>
       <c r="S4" t="n">
-        <v>77.90000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="T4" t="n">
-        <v>53.4</v>
+        <v>41.9</v>
       </c>
       <c r="U4" t="n">
-        <v>66</v>
+        <v>51.9</v>
       </c>
       <c r="V4" t="n">
-        <v>82.5</v>
+        <v>64.8</v>
       </c>
       <c r="W4" t="n">
-        <v>67.09999999999999</v>
+        <v>52.8</v>
       </c>
       <c r="X4" t="n">
-        <v>57.3</v>
+        <v>45</v>
       </c>
       <c r="Y4" t="n">
-        <v>57.2</v>
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
-        <v>63.3</v>
+        <v>49.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>74.90000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>65.09999999999999</v>
+        <v>51.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>74.90000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>115.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AE4" t="n">
-        <v>100.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>59.4</v>
+        <v>46.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>79.7</v>
+        <v>62.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>75.90000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>450</v>
+        <v>353.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>384.9</v>
+        <v>302.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>374.3</v>
+        <v>294.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>920.5</v>
+        <v>723.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>891.2</v>
+        <v>700.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>881.9</v>
+        <v>693.2</v>
       </c>
     </row>
     <row r="5">
@@ -4716,94 +4717,94 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>69.5</v>
+        <v>54.6</v>
       </c>
       <c r="L5" t="n">
-        <v>73.7</v>
+        <v>57.9</v>
       </c>
       <c r="M5" t="n">
-        <v>94.5</v>
+        <v>74.3</v>
       </c>
       <c r="N5" t="n">
-        <v>86.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="O5" t="n">
-        <v>55</v>
+        <v>43.2</v>
       </c>
       <c r="P5" t="n">
-        <v>68.5</v>
+        <v>53.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.2</v>
+        <v>49.6</v>
       </c>
       <c r="R5" t="n">
-        <v>87.5</v>
+        <v>68.7</v>
       </c>
       <c r="S5" t="n">
-        <v>78.59999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="T5" t="n">
-        <v>88.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>74.2</v>
+        <v>58.3</v>
       </c>
       <c r="V5" t="n">
-        <v>46.5</v>
+        <v>36.5</v>
       </c>
       <c r="W5" t="n">
-        <v>77.7</v>
+        <v>61.1</v>
       </c>
       <c r="X5" t="n">
-        <v>74.40000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>78.59999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>51.4</v>
+        <v>40.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>72.2</v>
+        <v>56.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>60.6</v>
+        <v>47.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>60.6</v>
+        <v>47.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>76.3</v>
+        <v>59.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>76.2</v>
+        <v>59.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>57.5</v>
+        <v>45.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>45.2</v>
+        <v>35.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>33.7</v>
+        <v>26.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>448.1</v>
+        <v>352.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>414.9</v>
+        <v>325.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>406.2</v>
+        <v>319</v>
       </c>
       <c r="AL5" t="n">
-        <v>886.7</v>
+        <v>696.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>764.4</v>
+        <v>600.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>769.6</v>
+        <v>604.5</v>
       </c>
     </row>
     <row r="6">
@@ -4858,94 +4859,94 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>66.5</v>
+        <v>52.2</v>
       </c>
       <c r="L6" t="n">
-        <v>87.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>107.2</v>
+        <v>84.2</v>
       </c>
       <c r="N6" t="n">
-        <v>99.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>86.2</v>
+        <v>67.8</v>
       </c>
       <c r="P6" t="n">
-        <v>83.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>63.3</v>
+        <v>49.7</v>
       </c>
       <c r="R6" t="n">
-        <v>73.09999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>58.9</v>
       </c>
       <c r="T6" t="n">
-        <v>67.90000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="U6" t="n">
-        <v>81.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="V6" t="n">
-        <v>74</v>
+        <v>58.2</v>
       </c>
       <c r="W6" t="n">
-        <v>96.3</v>
+        <v>75.7</v>
       </c>
       <c r="X6" t="n">
-        <v>114</v>
+        <v>89.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>102.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>97.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>87.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>66.5</v>
+        <v>52.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>89.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="AD6" t="n">
-        <v>99.7</v>
+        <v>78.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>74.7</v>
+        <v>58.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>111.1</v>
+        <v>87.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>85.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>96.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AI6" t="n">
-        <v>529.6</v>
+        <v>416.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>564.3</v>
+        <v>443.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>578.5</v>
+        <v>454.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>964.3</v>
+        <v>757.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>1121.4</v>
+        <v>881</v>
       </c>
       <c r="AN6" t="n">
-        <v>1132.3</v>
+        <v>889.5</v>
       </c>
     </row>
     <row r="7">
@@ -5000,94 +5001,94 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>103.7</v>
+        <v>81.5</v>
       </c>
       <c r="L7" t="n">
-        <v>77.8</v>
+        <v>61.2</v>
       </c>
       <c r="M7" t="n">
-        <v>92.5</v>
+        <v>72.7</v>
       </c>
       <c r="N7" t="n">
-        <v>73.5</v>
+        <v>57.7</v>
       </c>
       <c r="O7" t="n">
-        <v>80.3</v>
+        <v>63.1</v>
       </c>
       <c r="P7" t="n">
-        <v>103.7</v>
+        <v>81.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>121.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>72.7</v>
+        <v>57.2</v>
       </c>
       <c r="S7" t="n">
-        <v>87.8</v>
+        <v>69</v>
       </c>
       <c r="T7" t="n">
-        <v>104.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>76.5</v>
+        <v>60.1</v>
       </c>
       <c r="V7" t="n">
-        <v>100</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>85.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>110.1</v>
+        <v>86.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>107.2</v>
+        <v>84.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>120.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>105.9</v>
+        <v>83.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>78.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>111.1</v>
+        <v>87.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>80.2</v>
+        <v>63</v>
       </c>
       <c r="AE7" t="n">
-        <v>112.7</v>
+        <v>88.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="AG7" t="n">
-        <v>109.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>89.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>531.5</v>
+        <v>417.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>608.3</v>
+        <v>478</v>
       </c>
       <c r="AK7" t="n">
-        <v>573.4</v>
+        <v>450.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>1094.4</v>
+        <v>860.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>1238</v>
+        <v>972.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>1240.7</v>
+        <v>974.9</v>
       </c>
     </row>
     <row r="8">
@@ -5142,94 +5143,94 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>92.2</v>
+        <v>72.5</v>
       </c>
       <c r="L8" t="n">
-        <v>67.5</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>73.59999999999999</v>
+        <v>57.8</v>
       </c>
       <c r="N8" t="n">
-        <v>66.90000000000001</v>
+        <v>52.6</v>
       </c>
       <c r="O8" t="n">
-        <v>47.6</v>
+        <v>37.4</v>
       </c>
       <c r="P8" t="n">
-        <v>64.5</v>
+        <v>50.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>77</v>
+        <v>60.5</v>
       </c>
       <c r="R8" t="n">
-        <v>74.8</v>
+        <v>58.8</v>
       </c>
       <c r="S8" t="n">
-        <v>69.40000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="T8" t="n">
-        <v>41.2</v>
+        <v>32.4</v>
       </c>
       <c r="U8" t="n">
-        <v>89.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="V8" t="n">
-        <v>82.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>90.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>94.2</v>
+        <v>74</v>
       </c>
       <c r="Y8" t="n">
-        <v>69.09999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>66.8</v>
+        <v>52.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>80</v>
+        <v>62.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>99.5</v>
+        <v>78.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>51.3</v>
+        <v>40.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>72.2</v>
+        <v>56.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>65.2</v>
+        <v>51.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>83.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>96.5</v>
+        <v>75.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>71.2</v>
+        <v>56</v>
       </c>
       <c r="AI8" t="n">
-        <v>412.3</v>
+        <v>324</v>
       </c>
       <c r="AJ8" t="n">
-        <v>499.8</v>
+        <v>392.8</v>
       </c>
       <c r="AK8" t="n">
-        <v>499.4</v>
+        <v>392.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>846.3</v>
+        <v>665.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>939.7</v>
+        <v>738.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>944.6</v>
+        <v>742.3</v>
       </c>
     </row>
     <row r="9">
@@ -5284,94 +5285,94 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="L9" t="n">
-        <v>-30.4</v>
+        <v>-24.3</v>
       </c>
       <c r="M9" t="n">
-        <v>-38.6</v>
+        <v>-30.9</v>
       </c>
       <c r="N9" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="O9" t="n">
-        <v>-41.4</v>
+        <v>-33.1</v>
       </c>
       <c r="P9" t="n">
-        <v>-24.2</v>
+        <v>-19.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>-41.1</v>
+        <v>-32.9</v>
       </c>
       <c r="R9" t="n">
-        <v>-21.7</v>
+        <v>-17.3</v>
       </c>
       <c r="S9" t="n">
-        <v>-43.4</v>
+        <v>-34.7</v>
       </c>
       <c r="T9" t="n">
-        <v>-31.4</v>
+        <v>-25.1</v>
       </c>
       <c r="U9" t="n">
-        <v>-23.4</v>
+        <v>-18.7</v>
       </c>
       <c r="V9" t="n">
-        <v>-32.4</v>
+        <v>-25.9</v>
       </c>
       <c r="W9" t="n">
-        <v>-39.1</v>
+        <v>-31.3</v>
       </c>
       <c r="X9" t="n">
-        <v>-30.1</v>
+        <v>-24</v>
       </c>
       <c r="Y9" t="n">
-        <v>-33.4</v>
+        <v>-26.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>-38.6</v>
+        <v>-30.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>-35.6</v>
+        <v>-28.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-16</v>
+        <v>-12.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>-33.9</v>
+        <v>-27.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>-39.7</v>
+        <v>-31.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>-38.8</v>
+        <v>-31.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>-43.6</v>
+        <v>-34.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>-32.1</v>
+        <v>-25.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>-54.1</v>
+        <v>-43.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>-199.6</v>
+        <v>-159.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-192.8</v>
+        <v>-154.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>-182.6</v>
+        <v>-146.1</v>
       </c>
       <c r="AL9" t="n">
-        <v>-393</v>
+        <v>-314.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>-435</v>
+        <v>-348.2</v>
       </c>
       <c r="AN9" t="n">
-        <v>-423.3</v>
+        <v>-338.9</v>
       </c>
     </row>
     <row r="10">
@@ -5426,94 +5427,94 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-23.5</v>
+        <v>-18.8</v>
       </c>
       <c r="L10" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-20</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-20.2</v>
       </c>
-      <c r="M10" t="n">
-        <v>-27.8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-19</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-24.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="AC10" t="n">
         <v>-18</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-25.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-23.6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-24.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-26</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-23.7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-30.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-21.9</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-26.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-28.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-28.3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-31.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-22.5</v>
-      </c>
       <c r="AD10" t="n">
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="AE10" t="n">
-        <v>-26.8</v>
+        <v>-21.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>-19.8</v>
+        <v>-15.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>-24</v>
+        <v>-19.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>-34.3</v>
+        <v>-27.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>-128.8</v>
+        <v>-103.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-158.7</v>
+        <v>-127.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>-166.6</v>
+        <v>-133.4</v>
       </c>
       <c r="AL10" t="n">
-        <v>-282.1</v>
+        <v>-225.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>-316.1</v>
+        <v>-253.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>-309.1</v>
+        <v>-247.5</v>
       </c>
     </row>
     <row r="11">
@@ -5568,94 +5569,94 @@
         </is>
       </c>
       <c r="K11" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-36.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-22.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-39.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-33.7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-34.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-26.6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-29.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="AE11" t="n">
         <v>-26.5</v>
       </c>
-      <c r="L11" t="n">
-        <v>-31.3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-45.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-35.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-32.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-25.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-23.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-29.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-28</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-49.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-28.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-27.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-42.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-35.7</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-27.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-43.1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-33.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-27</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-37.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-38.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-33.1</v>
-      </c>
       <c r="AF11" t="n">
-        <v>-39.5</v>
+        <v>-31.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>-40.2</v>
+        <v>-32.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>-29.7</v>
+        <v>-23.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>-196.3</v>
+        <v>-157.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-208.7</v>
+        <v>-166.9</v>
       </c>
       <c r="AK11" t="n">
-        <v>-212.1</v>
+        <v>-169.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>-382.3</v>
+        <v>-305.8</v>
       </c>
       <c r="AM11" t="n">
-        <v>-426.6</v>
+        <v>-341.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>-456.1</v>
+        <v>-364.8</v>
       </c>
     </row>
     <row r="12">
@@ -5710,94 +5711,94 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-31</v>
+        <v>-24.8</v>
       </c>
       <c r="L12" t="n">
-        <v>-33</v>
+        <v>-26.4</v>
       </c>
       <c r="M12" t="n">
-        <v>-35.4</v>
+        <v>-28.3</v>
       </c>
       <c r="N12" t="n">
-        <v>-25.9</v>
+        <v>-20.7</v>
       </c>
       <c r="O12" t="n">
-        <v>-31.2</v>
+        <v>-25</v>
       </c>
       <c r="P12" t="n">
-        <v>-17.9</v>
+        <v>-14.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>-29.4</v>
+        <v>-23.5</v>
       </c>
       <c r="R12" t="n">
-        <v>-27.8</v>
+        <v>-22.3</v>
       </c>
       <c r="S12" t="n">
-        <v>-25.3</v>
+        <v>-20.2</v>
       </c>
       <c r="T12" t="n">
-        <v>-23.5</v>
+        <v>-18.8</v>
       </c>
       <c r="U12" t="n">
+        <v>-16</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-26.8</v>
+      </c>
+      <c r="X12" t="n">
         <v>-20</v>
       </c>
-      <c r="V12" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-25</v>
-      </c>
       <c r="Y12" t="n">
-        <v>-29.6</v>
+        <v>-23.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>-23.5</v>
+        <v>-18.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>-28.2</v>
+        <v>-22.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>-21.7</v>
+        <v>-17.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>-28.9</v>
+        <v>-23.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>-25.8</v>
+        <v>-20.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>-28.5</v>
+        <v>-22.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>-23.8</v>
+        <v>-19</v>
       </c>
       <c r="AG12" t="n">
-        <v>-20.8</v>
+        <v>-16.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>-25.2</v>
+        <v>-20.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>-174.4</v>
+        <v>-139.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-161.5</v>
+        <v>-129.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>-154.9</v>
+        <v>-124</v>
       </c>
       <c r="AL12" t="n">
-        <v>-326.9</v>
+        <v>-261.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>-314.5</v>
+        <v>-251.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>-329.1</v>
+        <v>-263.4</v>
       </c>
     </row>
   </sheetData>
@@ -6230,94 +6231,94 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>46</v>
+        <v>71.5</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="M3" t="n">
-        <v>27.5</v>
+        <v>42.8</v>
       </c>
       <c r="N3" t="n">
-        <v>42.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>32.2</v>
+        <v>50</v>
       </c>
       <c r="P3" t="n">
-        <v>49.3</v>
+        <v>76.7</v>
       </c>
       <c r="Q3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="R3" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="V3" t="n">
         <v>46.2</v>
       </c>
-      <c r="R3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T3" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="U3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>29.7</v>
-      </c>
       <c r="W3" t="n">
-        <v>47.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>40.2</v>
+        <v>62.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>38.1</v>
+        <v>59.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>33.9</v>
+        <v>52.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>31.4</v>
+        <v>48.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>36.1</v>
+        <v>56.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>64.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>41.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AE3" t="n">
-        <v>41.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>34.4</v>
+        <v>53.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>34.6</v>
+        <v>53.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>35.2</v>
+        <v>54.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>240.5</v>
+        <v>374.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>227</v>
+        <v>353.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>223.6</v>
+        <v>347.9</v>
       </c>
       <c r="AL3" t="n">
-        <v>471.3</v>
+        <v>733.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>477.8</v>
+        <v>743.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>480.5</v>
+        <v>747.5</v>
       </c>
     </row>
     <row r="4">
@@ -6372,94 +6373,94 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>30.4</v>
+        <v>47.3</v>
       </c>
       <c r="L4" t="n">
-        <v>46.9</v>
+        <v>73</v>
       </c>
       <c r="M4" t="n">
-        <v>39.3</v>
+        <v>61.2</v>
       </c>
       <c r="N4" t="n">
-        <v>44.8</v>
+        <v>69.7</v>
       </c>
       <c r="O4" t="n">
-        <v>38.7</v>
+        <v>60.2</v>
       </c>
       <c r="P4" t="n">
-        <v>32.5</v>
+        <v>50.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>49.1</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>36.1</v>
+        <v>56.2</v>
       </c>
       <c r="S4" t="n">
-        <v>38.4</v>
+        <v>59.7</v>
       </c>
       <c r="T4" t="n">
-        <v>32.5</v>
+        <v>50.6</v>
       </c>
       <c r="U4" t="n">
-        <v>41.2</v>
+        <v>64</v>
       </c>
       <c r="V4" t="n">
-        <v>36.5</v>
+        <v>56.7</v>
       </c>
       <c r="W4" t="n">
-        <v>41.7</v>
+        <v>64.8</v>
       </c>
       <c r="X4" t="n">
-        <v>42.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>52.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>28.3</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>46.7</v>
+        <v>72.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>45</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>30.4</v>
+        <v>47.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>44.2</v>
+        <v>68.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>42.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>41.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AH4" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>232.6</v>
+        <v>362</v>
       </c>
       <c r="AJ4" t="n">
-        <v>235.8</v>
+        <v>366.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>233.2</v>
+        <v>362.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>466.4</v>
+        <v>725.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>482.5</v>
+        <v>750.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>453.6</v>
+        <v>705.5</v>
       </c>
     </row>
     <row r="5">
@@ -6514,94 +6515,94 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>40.1</v>
+        <v>62.4</v>
       </c>
       <c r="L5" t="n">
-        <v>55.2</v>
+        <v>85.8</v>
       </c>
       <c r="M5" t="n">
-        <v>58.6</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>35.6</v>
+        <v>55.3</v>
       </c>
       <c r="O5" t="n">
-        <v>48.7</v>
+        <v>75.8</v>
       </c>
       <c r="P5" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.7</v>
+        <v>85</v>
       </c>
       <c r="R5" t="n">
-        <v>57.4</v>
+        <v>89.3</v>
       </c>
       <c r="S5" t="n">
-        <v>42.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>66.59999999999999</v>
+        <v>103.6</v>
       </c>
       <c r="U5" t="n">
-        <v>76.09999999999999</v>
+        <v>118.4</v>
       </c>
       <c r="V5" t="n">
-        <v>54.1</v>
+        <v>84.2</v>
       </c>
       <c r="W5" t="n">
-        <v>49.1</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>44.3</v>
+        <v>69</v>
       </c>
       <c r="Y5" t="n">
-        <v>67.40000000000001</v>
+        <v>104.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>58.6</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>48.4</v>
+        <v>75.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>71.09999999999999</v>
+        <v>110.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>66</v>
+        <v>102.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>64.2</v>
+        <v>99.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>37.5</v>
+        <v>58.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>56.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>64.40000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>43.6</v>
+        <v>67.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>301.2</v>
+        <v>468.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>338.9</v>
+        <v>527.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>325</v>
+        <v>505.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>652.3</v>
+        <v>1014.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>670.8</v>
+        <v>1043.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>695.8</v>
+        <v>1082.4</v>
       </c>
     </row>
     <row r="6">
@@ -6656,94 +6657,94 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>48</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>66.40000000000001</v>
+        <v>103.3</v>
       </c>
       <c r="M6" t="n">
-        <v>67</v>
+        <v>104.2</v>
       </c>
       <c r="N6" t="n">
-        <v>69.59999999999999</v>
+        <v>108.3</v>
       </c>
       <c r="O6" t="n">
-        <v>69.3</v>
+        <v>107.8</v>
       </c>
       <c r="P6" t="n">
-        <v>54.8</v>
+        <v>85.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>51.3</v>
+        <v>79.8</v>
       </c>
       <c r="R6" t="n">
-        <v>35.1</v>
+        <v>54.7</v>
       </c>
       <c r="S6" t="n">
-        <v>64.59999999999999</v>
+        <v>100.6</v>
       </c>
       <c r="T6" t="n">
-        <v>81.3</v>
+        <v>126.5</v>
       </c>
       <c r="U6" t="n">
-        <v>50.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>50.6</v>
+        <v>78.7</v>
       </c>
       <c r="W6" t="n">
-        <v>65.7</v>
+        <v>102.2</v>
       </c>
       <c r="X6" t="n">
-        <v>62.6</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>43.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>50.5</v>
+        <v>78.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>46.2</v>
+        <v>71.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>81</v>
+        <v>126.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>50.4</v>
+        <v>78.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>68</v>
+        <v>105.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>79.90000000000001</v>
+        <v>124.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>79.59999999999999</v>
+        <v>123.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>74.40000000000001</v>
+        <v>115.7</v>
       </c>
       <c r="AH6" t="n">
-        <v>76.7</v>
+        <v>119.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>375.1</v>
+        <v>583.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>349.1</v>
+        <v>543.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>350.9</v>
+        <v>545.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>708.7</v>
+        <v>1102.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>778.1</v>
+        <v>1210.6</v>
       </c>
       <c r="AN6" t="n">
-        <v>784.7</v>
+        <v>1220.9</v>
       </c>
     </row>
     <row r="7">
@@ -6798,94 +6799,94 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>71.09999999999999</v>
+        <v>110.6</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>48.2</v>
       </c>
       <c r="M7" t="n">
-        <v>51.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>35.1</v>
+        <v>54.6</v>
       </c>
       <c r="O7" t="n">
-        <v>59.1</v>
+        <v>92</v>
       </c>
       <c r="P7" t="n">
-        <v>58.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>65.90000000000001</v>
+        <v>102.6</v>
       </c>
       <c r="S7" t="n">
-        <v>47.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>58.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>49.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>41.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>42.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>44.6</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>51.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>46.9</v>
+        <v>73</v>
       </c>
       <c r="AA7" t="n">
-        <v>67.7</v>
+        <v>105.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>43.9</v>
+        <v>68.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>41.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>39</v>
+        <v>60.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>38.5</v>
+        <v>59.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>32.3</v>
+        <v>50.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.5</v>
+        <v>56.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>54.2</v>
+        <v>84.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>306.9</v>
+        <v>477.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>296.8</v>
+        <v>461.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>307.6</v>
+        <v>478.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>611.7</v>
+        <v>951.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>538.7</v>
+        <v>838.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>502.2</v>
+        <v>781.4</v>
       </c>
     </row>
     <row r="8">
@@ -6940,94 +6941,94 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>41.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>42.6</v>
+        <v>66.3</v>
       </c>
       <c r="M8" t="n">
-        <v>32.8</v>
+        <v>51</v>
       </c>
       <c r="N8" t="n">
-        <v>35</v>
+        <v>54.4</v>
       </c>
       <c r="O8" t="n">
-        <v>31.2</v>
+        <v>48.5</v>
       </c>
       <c r="P8" t="n">
-        <v>36.2</v>
+        <v>56.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.9</v>
+        <v>48</v>
       </c>
       <c r="R8" t="n">
-        <v>34.1</v>
+        <v>53.1</v>
       </c>
       <c r="S8" t="n">
-        <v>35.6</v>
+        <v>55.4</v>
       </c>
       <c r="T8" t="n">
-        <v>35.3</v>
+        <v>54.9</v>
       </c>
       <c r="U8" t="n">
-        <v>34.9</v>
+        <v>54.3</v>
       </c>
       <c r="V8" t="n">
-        <v>33.3</v>
+        <v>51.7</v>
       </c>
       <c r="W8" t="n">
-        <v>47.6</v>
+        <v>74</v>
       </c>
       <c r="X8" t="n">
-        <v>35.4</v>
+        <v>55</v>
       </c>
       <c r="Y8" t="n">
-        <v>30.4</v>
+        <v>47.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>39.3</v>
+        <v>61.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>29.9</v>
+        <v>46.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>30</v>
+        <v>46.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>38.5</v>
+        <v>59.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>25.6</v>
+        <v>39.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>14.2</v>
+        <v>22</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>62.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>45.5</v>
+        <v>70.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>25.6</v>
+        <v>39.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>219.2</v>
+        <v>340.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>212.6</v>
+        <v>330.8</v>
       </c>
       <c r="AK8" t="n">
-        <v>210.3</v>
+        <v>327.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>423.3</v>
+        <v>658.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>402</v>
+        <v>625.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>398.3</v>
+        <v>619.6</v>
       </c>
     </row>
     <row r="9">
@@ -7082,94 +7083,94 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-17.4</v>
+        <v>-23.7</v>
       </c>
       <c r="L9" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.8</v>
+        <v>-18.9</v>
       </c>
       <c r="N9" t="n">
-        <v>-27</v>
+        <v>-36.8</v>
       </c>
       <c r="O9" t="n">
-        <v>-22.2</v>
+        <v>-30.3</v>
       </c>
       <c r="P9" t="n">
-        <v>-24.3</v>
+        <v>-33.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>-21.4</v>
+        <v>-29.1</v>
       </c>
       <c r="R9" t="n">
-        <v>-13.2</v>
+        <v>-18</v>
       </c>
       <c r="S9" t="n">
-        <v>-22.2</v>
+        <v>-30.2</v>
       </c>
       <c r="T9" t="n">
-        <v>-16.7</v>
+        <v>-22.8</v>
       </c>
       <c r="U9" t="n">
-        <v>-22.9</v>
+        <v>-31.3</v>
       </c>
       <c r="V9" t="n">
-        <v>-19</v>
+        <v>-25.9</v>
       </c>
       <c r="W9" t="n">
-        <v>-24.4</v>
+        <v>-33.2</v>
       </c>
       <c r="X9" t="n">
-        <v>-24.8</v>
+        <v>-33.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>-29.3</v>
+        <v>-40</v>
       </c>
       <c r="Z9" t="n">
-        <v>-29.3</v>
+        <v>-40</v>
       </c>
       <c r="AA9" t="n">
-        <v>-21.2</v>
+        <v>-28.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>-25.7</v>
+        <v>-35.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>-32.5</v>
+        <v>-44.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>-28.1</v>
+        <v>-38.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>-22.5</v>
+        <v>-30.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>-25.2</v>
+        <v>-34.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>-24.2</v>
+        <v>-33</v>
       </c>
       <c r="AH9" t="n">
-        <v>-30.1</v>
+        <v>-41.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>-126.7</v>
+        <v>-172.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-154.7</v>
+        <v>-211.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>-149.8</v>
+        <v>-204.4</v>
       </c>
       <c r="AL9" t="n">
-        <v>-242.1</v>
+        <v>-330.1</v>
       </c>
       <c r="AM9" t="n">
-        <v>-317.3</v>
+        <v>-432.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>-298.1</v>
+        <v>-406.7</v>
       </c>
     </row>
     <row r="10">
@@ -7224,94 +7225,94 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-21.9</v>
+        <v>-29.8</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.9</v>
+        <v>-24.4</v>
       </c>
       <c r="M10" t="n">
-        <v>-18.7</v>
+        <v>-25.5</v>
       </c>
       <c r="N10" t="n">
-        <v>-32.1</v>
+        <v>-43.8</v>
       </c>
       <c r="O10" t="n">
-        <v>-29</v>
+        <v>-39.6</v>
       </c>
       <c r="P10" t="n">
-        <v>-36.4</v>
+        <v>-49.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>-16.6</v>
+        <v>-22.6</v>
       </c>
       <c r="R10" t="n">
-        <v>-22.6</v>
+        <v>-30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>-35.3</v>
+        <v>-48.2</v>
       </c>
       <c r="T10" t="n">
-        <v>-33.1</v>
+        <v>-45.1</v>
       </c>
       <c r="U10" t="n">
-        <v>-32.3</v>
+        <v>-44</v>
       </c>
       <c r="V10" t="n">
-        <v>-32.2</v>
+        <v>-43.9</v>
       </c>
       <c r="W10" t="n">
-        <v>-31.5</v>
+        <v>-43</v>
       </c>
       <c r="X10" t="n">
-        <v>-31.3</v>
+        <v>-42.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>-31.5</v>
+        <v>-43</v>
       </c>
       <c r="Z10" t="n">
-        <v>-36</v>
+        <v>-49</v>
       </c>
       <c r="AA10" t="n">
-        <v>-30.4</v>
+        <v>-41.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>-33.1</v>
+        <v>-45.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>-39.3</v>
+        <v>-53.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>-25.2</v>
+        <v>-34.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>-27.2</v>
+        <v>-37.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>-34.4</v>
+        <v>-47</v>
       </c>
       <c r="AG10" t="n">
-        <v>-29.9</v>
+        <v>-40.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>-30.5</v>
+        <v>-41.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>-156</v>
+        <v>-212.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-193.8</v>
+        <v>-264.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>-182.9</v>
+        <v>-249.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>-328.1</v>
+        <v>-447.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>-380.3</v>
+        <v>-518.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>-401.5</v>
+        <v>-547.5</v>
       </c>
     </row>
     <row r="11">
@@ -7366,94 +7367,94 @@
         </is>
       </c>
       <c r="K11" t="n">
+        <v>-39.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-23</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-27.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-38.1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-29.3</v>
       </c>
-      <c r="L11" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-19.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-17</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-27.9</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-21.5</v>
-      </c>
       <c r="R11" t="n">
-        <v>-17.9</v>
+        <v>-24.4</v>
       </c>
       <c r="S11" t="n">
-        <v>-21.4</v>
+        <v>-29.1</v>
       </c>
       <c r="T11" t="n">
-        <v>-16.4</v>
+        <v>-22.3</v>
       </c>
       <c r="U11" t="n">
-        <v>-17.1</v>
+        <v>-23.3</v>
       </c>
       <c r="V11" t="n">
-        <v>-19.9</v>
+        <v>-27.1</v>
       </c>
       <c r="W11" t="n">
-        <v>-29.4</v>
+        <v>-40.1</v>
       </c>
       <c r="X11" t="n">
-        <v>-11.4</v>
+        <v>-15.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>-21.8</v>
+        <v>-29.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>-25.4</v>
+        <v>-34.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>-23</v>
+        <v>-31.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>-27.6</v>
+        <v>-37.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>-21.9</v>
+        <v>-29.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>-20.7</v>
+        <v>-28.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>-19.6</v>
+        <v>-26.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>-16.8</v>
+        <v>-22.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>-26.5</v>
+        <v>-36.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>-15.5</v>
+        <v>-21.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>-126.1</v>
+        <v>-172.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-138.6</v>
+        <v>-189</v>
       </c>
       <c r="AK11" t="n">
-        <v>-142.1</v>
+        <v>-193.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>-240.3</v>
+        <v>-327.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>-259.6</v>
+        <v>-354.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>-246.3</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="12">
@@ -7508,94 +7509,94 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-22.7</v>
+        <v>-31</v>
       </c>
       <c r="L12" t="n">
-        <v>-25.3</v>
+        <v>-34.4</v>
       </c>
       <c r="M12" t="n">
-        <v>-25.3</v>
+        <v>-34.5</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.7</v>
+        <v>-39.2</v>
       </c>
       <c r="O12" t="n">
-        <v>-23.8</v>
+        <v>-32.4</v>
       </c>
       <c r="P12" t="n">
-        <v>-21.4</v>
+        <v>-29.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>-26.1</v>
+        <v>-35.6</v>
       </c>
       <c r="R12" t="n">
-        <v>-27.9</v>
+        <v>-38</v>
       </c>
       <c r="S12" t="n">
-        <v>-20.1</v>
+        <v>-27.5</v>
       </c>
       <c r="T12" t="n">
-        <v>-17.1</v>
+        <v>-23.3</v>
       </c>
       <c r="U12" t="n">
-        <v>-19.5</v>
+        <v>-26.7</v>
       </c>
       <c r="V12" t="n">
-        <v>-29.8</v>
+        <v>-40.6</v>
       </c>
       <c r="W12" t="n">
-        <v>-32.8</v>
+        <v>-44.8</v>
       </c>
       <c r="X12" t="n">
-        <v>-23.6</v>
+        <v>-32.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>-28.5</v>
+        <v>-38.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>-32</v>
+        <v>-43.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>-34.5</v>
+        <v>-47</v>
       </c>
       <c r="AB12" t="n">
-        <v>-24.7</v>
+        <v>-33.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>-26.7</v>
+        <v>-36.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>-34.9</v>
+        <v>-47.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>-39.8</v>
+        <v>-54.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>-35.4</v>
+        <v>-48.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>-22.3</v>
+        <v>-30.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>-30.1</v>
+        <v>-41.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>-147.2</v>
+        <v>-200.7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-176.1</v>
+        <v>-240.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>-176.8</v>
+        <v>-241</v>
       </c>
       <c r="AL12" t="n">
-        <v>-287.7</v>
+        <v>-392.4</v>
       </c>
       <c r="AM12" t="n">
-        <v>-365.3</v>
+        <v>-498.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>-342</v>
+        <v>-466.4</v>
       </c>
     </row>
   </sheetData>
@@ -8028,94 +8029,94 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>47.6</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8</v>
+        <v>54.4</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>51.8</v>
       </c>
       <c r="O3" t="n">
-        <v>4.3</v>
+        <v>47.9</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>45.5</v>
       </c>
       <c r="R3" t="n">
-        <v>5.3</v>
+        <v>59.5</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9</v>
+        <v>55.6</v>
       </c>
       <c r="T3" t="n">
-        <v>5.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>4.5</v>
+        <v>50.2</v>
       </c>
       <c r="V3" t="n">
-        <v>4.2</v>
+        <v>47.5</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8</v>
+        <v>31.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.5</v>
+        <v>50.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.7</v>
+        <v>30.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>61.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.6</v>
+        <v>41</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.2</v>
+        <v>47</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>34.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.8</v>
+        <v>42.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.4</v>
+        <v>38.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.1</v>
+        <v>57.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.4</v>
+        <v>49.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.2</v>
+        <v>35.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>27.3</v>
+        <v>307.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23.3</v>
+        <v>262.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>23.3</v>
+        <v>262.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>56.1</v>
+        <v>631.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>46.2</v>
+        <v>519.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.4</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4">
@@ -8170,94 +8171,94 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>55.9</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3</v>
+        <v>48.1</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5</v>
+        <v>51.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>44.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>44.3</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>45.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>56.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>54</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>32.8</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5</v>
+        <v>51</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>61.5</v>
       </c>
       <c r="W4" t="n">
-        <v>4.8</v>
+        <v>54.3</v>
       </c>
       <c r="X4" t="n">
-        <v>5.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.4</v>
+        <v>49.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.6</v>
+        <v>52</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.5</v>
+        <v>39</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.8</v>
+        <v>42.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>33.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.8</v>
+        <v>43</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.8</v>
+        <v>54.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>5.1</v>
+        <v>57.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.7</v>
+        <v>63.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.7</v>
+        <v>53.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>25.6</v>
+        <v>288.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.9</v>
+        <v>302.4</v>
       </c>
       <c r="AK4" t="n">
-        <v>26.7</v>
+        <v>300</v>
       </c>
       <c r="AL4" t="n">
-        <v>51.3</v>
+        <v>578.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>54</v>
+        <v>607.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>53.6</v>
+        <v>602.6</v>
       </c>
     </row>
     <row r="5">
@@ -8312,94 +8313,94 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4.8</v>
+        <v>53.7</v>
       </c>
       <c r="L5" t="n">
-        <v>4.1</v>
+        <v>46</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>29.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>34.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>40.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9</v>
+        <v>33.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>42.6</v>
       </c>
       <c r="R5" t="n">
-        <v>3.9</v>
+        <v>43.9</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>45.1</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>40.4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.8</v>
+        <v>31.8</v>
       </c>
       <c r="V5" t="n">
-        <v>2.9</v>
+        <v>32.1</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7</v>
+        <v>41.7</v>
       </c>
       <c r="X5" t="n">
-        <v>4.7</v>
+        <v>52.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.9</v>
+        <v>54.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>50.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>4</v>
+        <v>45.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.3</v>
+        <v>47.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.4</v>
+        <v>48.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.7</v>
+        <v>52.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>4.4</v>
+        <v>49.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.7</v>
+        <v>30.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.4</v>
+        <v>50</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.1</v>
+        <v>45.6</v>
       </c>
       <c r="AI5" t="n">
-        <v>21.2</v>
+        <v>237.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26.1</v>
+        <v>292.7</v>
       </c>
       <c r="AK5" t="n">
-        <v>25.7</v>
+        <v>287.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>42.2</v>
+        <v>473.1</v>
       </c>
       <c r="AM5" t="n">
-        <v>50.8</v>
+        <v>569.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.8</v>
+        <v>547.1</v>
       </c>
     </row>
     <row r="6">
@@ -8454,94 +8455,94 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>38.2</v>
       </c>
       <c r="L6" t="n">
-        <v>5.2</v>
+        <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>57.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>39.4</v>
       </c>
       <c r="P6" t="n">
-        <v>5.6</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.9</v>
+        <v>66</v>
       </c>
       <c r="R6" t="n">
-        <v>5.3</v>
+        <v>59.8</v>
       </c>
       <c r="S6" t="n">
-        <v>5.6</v>
+        <v>62.6</v>
       </c>
       <c r="T6" t="n">
-        <v>4.8</v>
+        <v>53.6</v>
       </c>
       <c r="U6" t="n">
-        <v>4.5</v>
+        <v>50.1</v>
       </c>
       <c r="V6" t="n">
-        <v>5.7</v>
+        <v>63.8</v>
       </c>
       <c r="W6" t="n">
-        <v>4.4</v>
+        <v>49.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>55.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.1</v>
+        <v>91.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.5</v>
+        <v>61.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.9</v>
+        <v>55.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.1</v>
+        <v>34.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.9</v>
+        <v>54.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.5</v>
+        <v>62.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>4</v>
+        <v>45.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.5</v>
+        <v>50.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>27.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.3</v>
+        <v>60.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>28.5</v>
+        <v>320.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>31</v>
+        <v>348.6</v>
       </c>
       <c r="AK6" t="n">
-        <v>30.5</v>
+        <v>342.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>60.3</v>
+        <v>676.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>57.7</v>
+        <v>649.9</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.4</v>
+        <v>635.1</v>
       </c>
     </row>
     <row r="7">
@@ -8596,94 +8597,94 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>5.4</v>
+        <v>60.9</v>
       </c>
       <c r="M7" t="n">
-        <v>4.9</v>
+        <v>55.6</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>54.7</v>
       </c>
       <c r="O7" t="n">
-        <v>4.3</v>
+        <v>48.1</v>
       </c>
       <c r="P7" t="n">
-        <v>6.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.1</v>
+        <v>68.2</v>
       </c>
       <c r="R7" t="n">
-        <v>4.1</v>
+        <v>46.3</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>67.8</v>
       </c>
       <c r="T7" t="n">
-        <v>4.4</v>
+        <v>49.5</v>
       </c>
       <c r="U7" t="n">
-        <v>3.6</v>
+        <v>40.5</v>
       </c>
       <c r="V7" t="n">
-        <v>6.4</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1</v>
+        <v>46.7</v>
       </c>
       <c r="X7" t="n">
-        <v>6.7</v>
+        <v>75.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.7</v>
+        <v>63.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>72</v>
       </c>
       <c r="AA7" t="n">
-        <v>6</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8</v>
+        <v>65.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>6.1</v>
+        <v>68.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>6.6</v>
+        <v>74.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.1</v>
+        <v>57</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.5</v>
+        <v>73.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.2</v>
+        <v>361.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>35.6</v>
+        <v>400</v>
       </c>
       <c r="AK7" t="n">
-        <v>37.7</v>
+        <v>423.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>62.8</v>
+        <v>705.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>71.40000000000001</v>
+        <v>802.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>73.2</v>
+        <v>822.7</v>
       </c>
     </row>
     <row r="8">
@@ -8738,94 +8739,94 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>51.6</v>
       </c>
       <c r="L8" t="n">
-        <v>5.1</v>
+        <v>57.7</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>51</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>45.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>54.5</v>
       </c>
       <c r="P8" t="n">
-        <v>5.1</v>
+        <v>56.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.2</v>
+        <v>58.3</v>
       </c>
       <c r="R8" t="n">
-        <v>5.6</v>
+        <v>62.6</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>35.4</v>
       </c>
       <c r="T8" t="n">
-        <v>6.2</v>
+        <v>70.3</v>
       </c>
       <c r="U8" t="n">
-        <v>4.7</v>
+        <v>52.9</v>
       </c>
       <c r="V8" t="n">
-        <v>4.1</v>
+        <v>46.3</v>
       </c>
       <c r="W8" t="n">
-        <v>4.3</v>
+        <v>48.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.1</v>
+        <v>57.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.6</v>
+        <v>62.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>49</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.9</v>
+        <v>54.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.2</v>
+        <v>35.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.9</v>
+        <v>54.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.6</v>
+        <v>51.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>4.3</v>
+        <v>48.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>5.6</v>
+        <v>62.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.7</v>
+        <v>64.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>28.1</v>
+        <v>316.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27.5</v>
+        <v>308.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>26.9</v>
+        <v>301.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>57</v>
+        <v>642.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>59.1</v>
+        <v>662.9</v>
       </c>
       <c r="AN8" t="n">
-        <v>61.3</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9">
@@ -8880,94 +8881,94 @@
         </is>
       </c>
       <c r="K9" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-24.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-24.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-22.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-26.6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="L9" t="n">
-        <v>-28.7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-29.2</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-27.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-25.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-24.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-31.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-23.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-25.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-22.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-23.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-26.7</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-27.4</v>
-      </c>
       <c r="AA9" t="n">
-        <v>-23</v>
+        <v>-19.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>-32.7</v>
+        <v>-27.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-20.2</v>
+        <v>-17.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>-27.4</v>
+        <v>-23.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>-27</v>
+        <v>-22.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>-21.7</v>
+        <v>-18.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>-23.3</v>
+        <v>-19.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>-29.2</v>
+        <v>-24.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>-158.9</v>
+        <v>-134.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-149.9</v>
+        <v>-126.8</v>
       </c>
       <c r="AK9" t="n">
-        <v>-144.8</v>
+        <v>-122.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>-311.2</v>
+        <v>-263.3</v>
       </c>
       <c r="AM9" t="n">
-        <v>-298.7</v>
+        <v>-252.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>-279.5</v>
+        <v>-236.5</v>
       </c>
     </row>
     <row r="10">
@@ -9022,94 +9023,94 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-12.4</v>
+        <v>-10.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.9</v>
+        <v>-13.4</v>
       </c>
       <c r="M10" t="n">
-        <v>-21.7</v>
+        <v>-18.3</v>
       </c>
       <c r="N10" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-17.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-18.1</v>
       </c>
-      <c r="O10" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-11.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-24.1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-18.7</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-17.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="AF10" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Y10" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-21.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-23.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-21.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-23.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-21.9</v>
-      </c>
       <c r="AG10" t="n">
-        <v>-16.3</v>
+        <v>-13.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>-22.2</v>
+        <v>-18.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>-94</v>
+        <v>-79.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-119.5</v>
+        <v>-101</v>
       </c>
       <c r="AK10" t="n">
-        <v>-114.7</v>
+        <v>-97</v>
       </c>
       <c r="AL10" t="n">
-        <v>-199.4</v>
+        <v>-168.4</v>
       </c>
       <c r="AM10" t="n">
-        <v>-240.6</v>
+        <v>-203.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>-246.2</v>
+        <v>-208.3</v>
       </c>
     </row>
     <row r="11">
@@ -9164,94 +9165,94 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-19.4</v>
+        <v>-16.4</v>
       </c>
       <c r="L11" t="n">
-        <v>-25.8</v>
+        <v>-21.8</v>
       </c>
       <c r="M11" t="n">
-        <v>-25.3</v>
+        <v>-21.4</v>
       </c>
       <c r="N11" t="n">
-        <v>-26.7</v>
+        <v>-22.6</v>
       </c>
       <c r="O11" t="n">
-        <v>-20.3</v>
+        <v>-17.1</v>
       </c>
       <c r="P11" t="n">
-        <v>-16.6</v>
+        <v>-14.1</v>
       </c>
       <c r="Q11" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-20</v>
+      </c>
+      <c r="W11" t="n">
         <v>-21.6</v>
       </c>
-      <c r="R11" t="n">
-        <v>-21</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-18.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-24.6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-26.1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-23.7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-25.5</v>
-      </c>
       <c r="X11" t="n">
-        <v>-22.4</v>
+        <v>-18.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>-16.4</v>
+        <v>-13.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>-18.1</v>
+        <v>-15.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>-19.1</v>
+        <v>-16.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>-23.6</v>
+        <v>-20</v>
       </c>
       <c r="AC11" t="n">
-        <v>-24.7</v>
+        <v>-20.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>-21.3</v>
+        <v>-18</v>
       </c>
       <c r="AE11" t="n">
-        <v>-25.1</v>
+        <v>-21.2</v>
       </c>
       <c r="AF11" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="AG11" t="n">
         <v>-17.1</v>
       </c>
-      <c r="AG11" t="n">
-        <v>-20.2</v>
-      </c>
       <c r="AH11" t="n">
-        <v>-27.2</v>
+        <v>-23</v>
       </c>
       <c r="AI11" t="n">
-        <v>-134.1</v>
+        <v>-113.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-125.1</v>
+        <v>-105.9</v>
       </c>
       <c r="AK11" t="n">
-        <v>-120.4</v>
+        <v>-101.9</v>
       </c>
       <c r="AL11" t="n">
-        <v>-269.8</v>
+        <v>-228.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>-260.7</v>
+        <v>-220.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>-259.6</v>
+        <v>-219.7</v>
       </c>
     </row>
     <row r="12">
@@ -9306,94 +9307,1892 @@
         </is>
       </c>
       <c r="K12" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-31.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-19</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-137.3</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-171.7</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-161.4</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-284.5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-334.6</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-336.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Actuals</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MICA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MICA_Level_4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MICA_Level_3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MICA_Level_2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MICA_Level_1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Product_code</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Product_Level_3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Product_Level_2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Product_Level_1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Entity code</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Jan-25</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Feb-25</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Mar-25</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Apr-25</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>May-25</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Jun-25</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Jul-25</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aug-25</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Sep-25</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Oct-25</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Nov-25</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Dec-25</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Oct-26</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Nov-26</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Dec-26</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>JUN YTD-25</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>JUN YTD-26</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>JUN YTD-26 Target</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>FY-25</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>FY-26 Forecast</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>FY-26 Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MP10101010000</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NII - Interest Income</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MP10101010000</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NII - Interest Income</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NII - Net Interest Income</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MP10201010000</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NFI - Fee Income</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Net Fee Income</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MP10201010000</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NFI - Fee Income</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Net Fee Income</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>58</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MP10301010000</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Insurance Manufacturing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Net Insurance Revenue</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MP10301010000</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Insurance Manufacturing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Net Insurance Revenue</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MP20101010000</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Total Direct Cost</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-34.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-37.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-23</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-26.8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-40.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-30.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-37.7</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-38.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-30.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-38.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-36.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-33.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-28.9</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-31.7</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-29.7</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-185.9</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-211.6</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-201.6</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-367.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-393.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-373.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MP20101010000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Total Direct Cost</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-24</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-34.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-32.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-29.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-28.9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-23.3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="AC10" t="n">
         <v>-23.1</v>
       </c>
+      <c r="AD10" t="n">
+        <v>-31.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-28.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-132.7</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-140.9</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-149.2</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-310.2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-300.2</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-285.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MP30101010000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-33</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-36.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-35.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-25.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-22.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-22.4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-24.1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-145.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-151.2</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-159</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-313.5</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-300.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-285.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MP30101010000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Expected credit losses</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>-25.2</v>
+      </c>
       <c r="L12" t="n">
-        <v>-33.3</v>
+        <v>-21.1</v>
       </c>
       <c r="M12" t="n">
-        <v>-36.7</v>
+        <v>-24.2</v>
       </c>
       <c r="N12" t="n">
-        <v>-24.4</v>
+        <v>-10.2</v>
       </c>
       <c r="O12" t="n">
-        <v>-22.4</v>
+        <v>-17.1</v>
       </c>
       <c r="P12" t="n">
-        <v>-22.2</v>
+        <v>-31.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>-22.9</v>
+        <v>-36.4</v>
       </c>
       <c r="R12" t="n">
-        <v>-30.9</v>
+        <v>-36.6</v>
       </c>
       <c r="S12" t="n">
-        <v>-26.1</v>
+        <v>-21.8</v>
       </c>
       <c r="T12" t="n">
-        <v>-38.1</v>
+        <v>-25.7</v>
       </c>
       <c r="U12" t="n">
-        <v>-31.8</v>
+        <v>-29.5</v>
       </c>
       <c r="V12" t="n">
-        <v>-24.1</v>
+        <v>-19.3</v>
       </c>
       <c r="W12" t="n">
-        <v>-33</v>
+        <v>-38.2</v>
       </c>
       <c r="X12" t="n">
-        <v>-30.8</v>
+        <v>-25.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>-36</v>
+        <v>-31.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>-36.7</v>
+        <v>-23.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>-29.8</v>
+        <v>-31.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>-36.6</v>
+        <v>-29.2</v>
       </c>
       <c r="AC12" t="n">
         <v>-34.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>-31.2</v>
+        <v>-23.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>-33.1</v>
+        <v>-29.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>-35.4</v>
+        <v>-38.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>-30</v>
+        <v>-23.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>-28</v>
+        <v>-31.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>-162.1</v>
+        <v>-129.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-202.9</v>
+        <v>-178.8</v>
       </c>
       <c r="AK12" t="n">
-        <v>-190.7</v>
+        <v>-186.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>-336</v>
+        <v>-298.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>-395.4</v>
+        <v>-359.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>-397.8</v>
+        <v>-343.9</v>
       </c>
     </row>
   </sheetData>
